--- a/src/initial_clustered_matrix.xlsx
+++ b/src/initial_clustered_matrix.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Guest Profile</t>
+          <t>Customer Profile</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Reservation</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Reservation</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Financial Statement</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -513,44 +513,34 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Waste Record</t>
+          <t>Inventory Record</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Inventory Record</t>
+          <t>Compliance Log</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>HACCP Record</t>
+          <t>Recipe</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>Menu</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Menu</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
           <t>Strategic Plan</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Financial Statement</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Premium Take-away and Delivery Fulfillment Process</t>
+          <t>Kitchen Production and Service Preparation Process</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -558,37 +548,35 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Dine-In Service Delivery and Guest Experience Process</t>
+          <t>Premium Take-away and Delivery Fulfillment Process</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -598,41 +586,43 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Marketing, Loyalty and CRM Process</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>Dine-In Service Delivery and Guest Experience Process</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -640,16 +630,12 @@
           <t>R</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -658,37 +644,35 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Reservation, Table and Capacity Management Process</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>Marketing, Loyalty and CRM Process</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -696,13 +680,11 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Events and B2B Process</t>
+          <t>Reservation, Table and Capacity Management Process</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -710,159 +692,147 @@
           <t>R</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Supplier and Procurement Management Process</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>Events and B2B Process</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Inventory and Storage Management Process</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>Financial Management and Compliance Process</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>U</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Kitchen Production and Service Preparation Process</t>
+          <t>Supplier and Procurement Management Process</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Quality, Food Safety and Risk Management Process</t>
+          <t>Inventory and Storage Management Process</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -873,34 +843,32 @@
           <t>R</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Menu, Product and Experience Design Process</t>
+          <t>Quality, Food Safety and Risk Management Process</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -911,36 +879,34 @@
           <t>R</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Strategic Planning and Governance Process</t>
+          <t>Menu, Product and Experience Design Process</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -949,33 +915,31 @@
           <t>R</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Financial Management and Compliance Process</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>Strategic Planning and Governance Process</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -986,18 +950,20 @@
           <t>R</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
